--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -206,241 +206,241 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>ANASTACIO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
     <t>NUBE</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
     <t>ALEMAN</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
     <t>HIRAM FABIAN</t>
   </si>
   <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
     <t>CHRISTIAN YAIR</t>
   </si>
   <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CESAR OMAR</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
     <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CESAR OMAR</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
   </si>
   <si>
     <t>ALEXANDER</t>
@@ -966,25 +966,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1008,10 +1008,10 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1055,25 +1055,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1097,16 +1097,16 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>9</v>
@@ -1144,25 +1144,25 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1195,16 +1195,16 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1224,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1233,25 +1233,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1287,13 +1287,13 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1322,25 +1322,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1364,13 +1364,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1382,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1411,25 +1411,25 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1456,22 +1456,22 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>9</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1500,25 +1500,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1542,7 +1542,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1560,7 +1560,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1589,25 +1589,25 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1631,7 +1631,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1643,13 +1643,13 @@
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1678,25 +1678,25 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1720,10 +1720,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1767,25 +1767,25 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1809,7 +1809,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1821,13 +1821,13 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1856,25 +1856,25 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1898,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1916,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1945,25 +1945,25 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1996,7 +1996,7 @@
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>10</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2034,25 +2034,25 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2076,25 +2076,25 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2123,25 +2123,25 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2165,16 +2165,16 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2183,7 +2183,7 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2212,25 +2212,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2254,7 +2254,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2263,7 +2263,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2301,25 +2301,25 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2355,7 +2355,7 @@
         <v>7</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>10</v>
@@ -2390,25 +2390,25 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2432,16 +2432,16 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2479,25 +2479,25 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2521,13 +2521,13 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2539,7 +2539,7 @@
         <v>10</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2559,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2568,25 +2568,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2622,13 +2622,13 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2657,25 +2657,25 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2699,25 +2699,25 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2746,25 +2746,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2788,13 +2788,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -2806,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2835,25 +2835,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2877,25 +2877,25 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB25">
         <v>6</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2924,25 +2924,25 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2966,7 +2966,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2978,13 +2978,13 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3013,25 +3013,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3064,7 +3064,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -3073,7 +3073,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3102,25 +3102,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3144,16 +3144,16 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28">
         <v>10</v>
@@ -3162,7 +3162,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3191,25 +3191,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3233,25 +3233,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB29">
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3280,25 +3280,25 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3334,13 +3334,13 @@
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3360,7 +3360,7 @@
         <v>5</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3369,25 +3369,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3423,13 +3423,13 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB31">
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3458,25 +3458,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3500,7 +3500,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3509,7 +3509,7 @@
         <v>9</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -3518,7 +3518,7 @@
         <v>10</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3583,19 +3583,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>53.33</v>
+        <v>63.33</v>
       </c>
       <c r="G2">
-        <v>46.67</v>
+        <v>36.67</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3659,7 +3659,7 @@
         <v>16.67</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3679,30 +3679,30 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3723,7 +3723,7 @@
         <v>6.67</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -3743,19 +3743,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="G7">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3803,7 +3803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3828,66 +3828,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920042</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920069</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3923,64 +3863,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920042</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920100</v>
+        <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920069</v>
+        <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920039</v>
+        <v>20330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>116</v>
@@ -3991,13 +3931,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>117</v>
@@ -4008,13 +3948,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920043</v>
+        <v>20330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
@@ -4025,13 +3965,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920044</v>
+        <v>20330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
@@ -4042,13 +3982,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920045</v>
+        <v>20330051920048</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -4059,13 +3999,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920046</v>
+        <v>20330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
@@ -4076,16 +4016,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920048</v>
+        <v>20330051920051</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4093,16 +4033,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920050</v>
+        <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4110,16 +4050,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920051</v>
+        <v>20330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4127,13 +4067,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920365</v>
+        <v>20330051920053</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>124</v>
@@ -4144,13 +4084,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920052</v>
+        <v>20330051920056</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>125</v>
@@ -4161,13 +4101,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920053</v>
+        <v>20330051920057</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>126</v>
@@ -4178,13 +4118,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920056</v>
+        <v>20330051920095</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>127</v>
@@ -4195,13 +4135,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920057</v>
+        <v>20330051920096</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>128</v>
@@ -4212,13 +4152,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920095</v>
+        <v>20330051920097</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>129</v>
@@ -4229,13 +4169,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920096</v>
+        <v>20330051920099</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
         <v>130</v>
@@ -4246,13 +4183,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920097</v>
+        <v>20330051920100</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
@@ -4263,10 +4200,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920099</v>
+        <v>20330051920101</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
       </c>
       <c r="D22" t="s">
         <v>132</v>
@@ -4277,13 +4217,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920101</v>
+        <v>20330051920102</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4294,13 +4234,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920102</v>
+        <v>20330051920058</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
@@ -4311,13 +4251,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920058</v>
+        <v>20330051920104</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>135</v>
@@ -4328,13 +4268,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920104</v>
+        <v>20330051920105</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
@@ -4345,10 +4285,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920105</v>
+        <v>20330051920107</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
         <v>86</v>
@@ -4362,13 +4302,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920107</v>
+        <v>20330051920111</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>138</v>
@@ -4379,13 +4319,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
@@ -4396,13 +4336,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920112</v>
+        <v>20330051920069</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
         <v>140</v>
@@ -4416,10 +4356,10 @@
         <v>20330051920113</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -4435,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4467,22 +4407,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920097</v>
+        <v>20330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4490,22 +4430,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920097</v>
+        <v>20330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4513,16 +4453,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920112</v>
+        <v>20330051920044</v>
       </c>
       <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4536,22 +4476,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920112</v>
+        <v>20330051920046</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4559,22 +4499,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920039</v>
+        <v>20330051920050</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4582,22 +4522,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920040</v>
+        <v>20330051920365</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4605,16 +4545,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920044</v>
+        <v>20330051920052</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4628,16 +4568,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920046</v>
+        <v>20330051920096</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4651,22 +4591,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920050</v>
+        <v>20330051920097</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4674,22 +4614,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920365</v>
+        <v>20330051920058</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4697,16 +4637,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920052</v>
+        <v>20330051920104</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4720,70 +4660,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920096</v>
+        <v>20330051920111</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920104</v>
-      </c>
-      <c r="B14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920111</v>
-      </c>
-      <c r="B15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -981,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -1070,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>9</v>
@@ -1112,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1159,7 +1159,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -1201,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1248,7 +1248,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1337,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1379,7 +1379,7 @@
         <v>10</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1426,7 +1426,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1468,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1515,7 +1515,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>7</v>
@@ -1604,7 +1604,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -1646,7 +1646,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1693,7 +1693,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1782,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -1871,7 +1871,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1913,7 +1913,7 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -1960,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -2049,7 +2049,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>8</v>
@@ -2091,7 +2091,7 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>9</v>
@@ -2138,7 +2138,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -2180,7 +2180,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -2227,7 +2227,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -2316,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2405,7 +2405,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2494,7 +2494,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2583,7 +2583,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2672,7 +2672,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -2714,7 +2714,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>7</v>
@@ -2803,7 +2803,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -2850,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>5</v>
@@ -2892,7 +2892,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2939,7 +2939,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2981,7 +2981,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3028,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>8</v>
@@ -3070,7 +3070,7 @@
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>9</v>
@@ -3117,7 +3117,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>8</v>
@@ -3248,7 +3248,7 @@
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3295,7 +3295,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>6</v>
@@ -3337,7 +3337,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3384,7 +3384,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>5</v>
@@ -3473,7 +3473,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3615,19 +3615,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4375,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920112</v>
+        <v>20330051920101</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4430,22 +4430,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920112</v>
+        <v>20330051920101</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4453,22 +4453,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920044</v>
+        <v>20330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4476,22 +4476,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920046</v>
+        <v>20330051920058</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920050</v>
+        <v>20330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4522,22 +4522,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920365</v>
+        <v>20330051920111</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4545,16 +4545,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920052</v>
+        <v>20330051920044</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4568,16 +4568,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920096</v>
+        <v>20330051920046</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4591,22 +4591,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920097</v>
+        <v>20330051920365</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4614,22 +4614,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920058</v>
+        <v>20330051920052</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4637,16 +4637,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920104</v>
+        <v>20330051920096</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4660,24 +4660,70 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920111</v>
+        <v>20330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920104</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920112</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -999,7 +999,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1088,7 +1088,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1177,7 +1177,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1266,7 +1266,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1355,7 +1355,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1444,7 +1444,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1533,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1554,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1622,7 +1622,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1643,7 +1643,7 @@
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1711,7 +1711,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1800,7 +1800,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1821,7 +1821,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>8</v>
@@ -1889,7 +1889,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>6</v>
@@ -1978,7 +1978,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -2067,7 +2067,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2088,7 +2088,7 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2334,7 +2334,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2355,7 +2355,7 @@
         <v>7</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2601,7 +2601,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2779,7 +2779,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2800,7 +2800,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -2957,7 +2957,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2978,7 +2978,7 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -3046,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3135,7 +3135,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3313,7 +3313,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3402,7 +3402,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3691,7 +3691,7 @@
         <v>16.67</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,10 +179,10 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
@@ -990,7 +990,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1079,7 +1079,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1168,7 +1168,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1189,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1257,7 +1257,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1346,7 +1346,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1367,7 +1367,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1435,7 +1435,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1456,7 +1456,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1545,7 +1545,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1613,7 +1613,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1634,7 +1634,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1702,7 +1702,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1791,7 +1791,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1812,7 +1812,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1880,7 +1880,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1901,7 +1901,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1969,7 +1969,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -2058,7 +2058,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2147,7 +2147,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2168,7 +2168,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2236,7 +2236,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2325,7 +2325,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2346,7 +2346,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2414,7 +2414,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2435,7 +2435,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2503,7 +2503,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2592,7 +2592,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2681,7 +2681,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2702,7 +2702,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2770,7 +2770,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2859,7 +2859,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2948,7 +2948,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3126,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3215,7 +3215,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3304,7 +3304,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3393,7 +3393,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3482,7 +3482,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3503,7 +3503,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3659,7 +3659,7 @@
         <v>16.67</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3679,19 +3679,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4375,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4422,7 +4422,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4468,7 +4468,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4514,7 +4514,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4591,22 +4591,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920365</v>
+        <v>20330051920052</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4614,16 +4614,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920052</v>
+        <v>20330051920096</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4637,16 +4637,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920096</v>
+        <v>20330051920097</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4660,16 +4660,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920097</v>
+        <v>20330051920104</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4683,16 +4683,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920104</v>
+        <v>20330051920112</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4701,29 +4701,6 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920112</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,13 +179,13 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -993,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1005,7 +1005,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1094,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1171,7 +1171,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1183,7 +1183,7 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1192,7 +1192,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -1260,7 +1260,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1272,7 +1272,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1281,7 +1281,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1293,7 +1293,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1361,7 +1361,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1438,7 +1438,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1450,7 +1450,7 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1459,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1527,7 +1527,7 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1539,7 +1539,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1560,7 +1560,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1628,7 +1628,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1649,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1705,7 +1705,7 @@
         <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1717,7 +1717,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1806,7 +1806,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1815,7 +1815,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1883,7 +1883,7 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1904,7 +1904,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1916,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1972,7 +1972,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1984,7 +1984,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2061,7 +2061,7 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2073,7 +2073,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2082,7 +2082,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -2150,19 +2150,19 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2239,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2251,7 +2251,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2272,7 +2272,7 @@
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2328,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2340,7 +2340,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2417,7 +2417,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2429,7 +2429,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2506,19 +2506,19 @@
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2527,19 +2527,19 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2595,7 +2595,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2607,7 +2607,7 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2628,7 +2628,7 @@
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2684,7 +2684,7 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2696,7 +2696,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2717,7 +2717,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2785,7 +2785,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2794,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -2806,7 +2806,7 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2862,19 +2862,19 @@
         <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2883,19 +2883,19 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2951,7 +2951,7 @@
         <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2963,7 +2963,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2972,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -3040,7 +3040,7 @@
         <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -3052,7 +3052,7 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -3129,7 +3129,7 @@
         <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3141,7 +3141,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3218,19 +3218,19 @@
         <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3245,13 +3245,13 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3307,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3319,7 +3319,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3328,7 +3328,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z30">
         <v>5</v>
@@ -3340,7 +3340,7 @@
         <v>6</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3396,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3408,7 +3408,7 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3429,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3485,19 +3485,19 @@
         <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3506,19 +3506,19 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>9</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -3647,19 +3647,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="G4">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3691,7 +3691,7 @@
         <v>13.33</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3711,16 +3711,16 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>93.33</v>
+        <v>90</v>
       </c>
       <c r="G6">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -3775,19 +3775,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4375,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4407,19 +4407,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920101</v>
+        <v>20330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -4430,16 +4430,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920101</v>
+        <v>20330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4453,22 +4453,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920058</v>
+        <v>20330051920044</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4476,22 +4476,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920058</v>
+        <v>20330051920046</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920111</v>
+        <v>20330051920052</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4522,22 +4522,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920111</v>
+        <v>20330051920096</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4545,16 +4545,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920044</v>
+        <v>20330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920046</v>
+        <v>20330051920058</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4591,16 +4591,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920052</v>
+        <v>20330051920104</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4614,93 +4614,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920096</v>
+        <v>20330051920111</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920097</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920104</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -987,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1085,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1165,7 +1165,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -1174,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1195,7 +1195,7 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1254,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1263,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1343,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1373,7 +1373,7 @@
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1432,7 +1432,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -1441,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1462,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>8</v>
@@ -1521,7 +1521,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1542,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1610,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -1619,7 +1619,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1631,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1640,7 +1640,7 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -1699,7 +1699,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1708,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1788,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -1797,7 +1797,7 @@
         <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1818,7 +1818,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>6</v>
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -1886,7 +1886,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1898,7 +1898,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1907,7 +1907,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -1966,7 +1966,7 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1975,7 +1975,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1987,7 +1987,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1996,7 +1996,7 @@
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -2055,7 +2055,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>6</v>
@@ -2064,7 +2064,7 @@
         <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -2085,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -2144,7 +2144,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2233,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2242,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2263,7 +2263,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2322,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2331,7 +2331,7 @@
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2411,7 +2411,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2420,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2500,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2509,7 +2509,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2521,7 +2521,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2530,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -2598,7 +2598,7 @@
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2610,7 +2610,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2678,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>6</v>
@@ -2687,7 +2687,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2767,7 +2767,7 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2776,7 +2776,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2788,7 +2788,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2856,7 +2856,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2865,7 +2865,7 @@
         <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2877,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2945,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -2954,7 +2954,7 @@
         <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2966,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2975,7 +2975,7 @@
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -3034,7 +3034,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>6</v>
@@ -3043,7 +3043,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -3123,7 +3123,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>9</v>
@@ -3132,7 +3132,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -3144,7 +3144,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -3153,7 +3153,7 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3221,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3233,7 +3233,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3242,7 +3242,7 @@
         <v>8</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3301,7 +3301,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -3310,7 +3310,7 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3322,7 +3322,7 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3331,7 +3331,7 @@
         <v>5</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>8</v>
@@ -3390,7 +3390,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>5</v>
@@ -3399,7 +3399,7 @@
         <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3479,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -3488,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -3500,7 +3500,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3509,7 +3509,7 @@
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>8</v>
@@ -3583,16 +3583,16 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>63.33</v>
+        <v>76.67</v>
       </c>
       <c r="G2">
-        <v>36.67</v>
+        <v>23.33</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -3743,19 +3743,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>96.67</v>
+        <v>93.33</v>
       </c>
       <c r="G7">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4375,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920112</v>
+        <v>20330051920111</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4430,22 +4430,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920112</v>
+        <v>20330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4453,16 +4453,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920044</v>
+        <v>20330051920040</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4476,16 +4476,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920046</v>
+        <v>20330051920050</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920052</v>
+        <v>20330051920058</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4522,116 +4522,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920096</v>
+        <v>20330051920112</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920097</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920058</v>
-      </c>
-      <c r="B9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920104</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920111</v>
-      </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20221.xlsx
+++ b/grupos/5BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -1002,7 +1002,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -1091,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1112,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1447,7 +1447,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1468,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1536,7 +1536,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1625,7 +1625,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1714,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1803,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1892,7 +1892,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1913,7 +1913,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -2070,7 +2070,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2180,7 +2180,7 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -2248,7 +2248,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2337,7 +2337,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2426,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2447,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -2515,7 +2515,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2604,7 +2604,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2693,7 +2693,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2714,7 +2714,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2782,7 +2782,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2803,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2871,7 +2871,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2960,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -3049,7 +3049,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -3138,7 +3138,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -3227,7 +3227,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3248,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3316,7 +3316,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3337,7 +3337,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>7</v>
@@ -3405,7 +3405,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>2</v>
@@ -3494,7 +3494,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -3615,16 +3615,16 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="G3">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="H3">
         <v>7.8</v>
@@ -4375,7 +4375,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4407,16 +4407,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920111</v>
+        <v>20330051920040</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4430,22 +4430,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920111</v>
+        <v>20330051920050</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4453,22 +4453,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920040</v>
+        <v>20330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4476,16 +4476,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920050</v>
+        <v>20330051920111</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4499,47 +4499,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920058</v>
+        <v>20330051920112</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920112</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>
